--- a/Stats Sheet/Round Gaps/Azure.xlsx
+++ b/Stats Sheet/Round Gaps/Azure.xlsx
@@ -76,6 +76,9 @@
     <x:t>19</x:t>
   </x:si>
   <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
     <x:t>_JJL</x:t>
   </x:si>
   <x:si>
@@ -103,12 +106,12 @@
     <x:t>688</x:t>
   </x:si>
   <x:si>
+    <x:t>79</x:t>
+  </x:si>
+  <x:si>
     <x:t>ConBeanJones</x:t>
   </x:si>
   <x:si>
-    <x:t>79</x:t>
-  </x:si>
-  <x:si>
     <x:t>2218</x:t>
   </x:si>
   <x:si>
@@ -127,6 +130,9 @@
     <x:t>764</x:t>
   </x:si>
   <x:si>
+    <x:t>356</x:t>
+  </x:si>
+  <x:si>
     <x:t>JRjoos</x:t>
   </x:si>
   <x:si>
@@ -169,6 +175,9 @@
     <x:t>IceshardEleven</x:t>
   </x:si>
   <x:si>
+    <x:t>3345</x:t>
+  </x:si>
+  <x:si>
     <x:t>Iplayball</x:t>
   </x:si>
   <x:si>
@@ -196,12 +205,18 @@
     <x:t>902</x:t>
   </x:si>
   <x:si>
+    <x:t>277</x:t>
+  </x:si>
+  <x:si>
     <x:t>JasonBPE</x:t>
   </x:si>
   <x:si>
     <x:t>2225</x:t>
   </x:si>
   <x:si>
+    <x:t>1120</x:t>
+  </x:si>
+  <x:si>
     <x:t>ParkMc</x:t>
   </x:si>
   <x:si>
@@ -235,7 +250,10 @@
     <x:t>1091</x:t>
   </x:si>
   <x:si>
-    <x:t>LqndSlide</x:t>
+    <x:t>lqndslide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3464</x:t>
   </x:si>
   <x:si>
     <x:t>Magiclz</x:t>
@@ -382,6 +400,9 @@
     <x:t>Chasmic</x:t>
   </x:si>
   <x:si>
+    <x:t>1808</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fensua</x:t>
   </x:si>
   <x:si>
@@ -433,6 +454,9 @@
     <x:t>Kaismartypants</x:t>
   </x:si>
   <x:si>
+    <x:t>632</x:t>
+  </x:si>
+  <x:si>
     <x:t>Kelawesome</x:t>
   </x:si>
   <x:si>
@@ -496,6 +520,9 @@
     <x:t>kirbey</x:t>
   </x:si>
   <x:si>
+    <x:t>1179</x:t>
+  </x:si>
+  <x:si>
     <x:t>natsuvi</x:t>
   </x:si>
   <x:si>
@@ -617,6 +644,42 @@
   </x:si>
   <x:si>
     <x:t>automavic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5kylord</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arradir</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brodator</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyclops</x:t>
+  </x:si>
+  <x:si>
+    <x:t>megatallicayer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ohh_lia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ozzyowo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ProGirlGamer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ratchet6859</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TonyEatWorld</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wizarde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>yistv2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -975,10 +1038,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:X134"/>
+  <x:dimension ref="A1:Y146"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:24" s="1" customFormat="1">
+    <x:row r="1" spans="1:25" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>42434</x:v>
       </x:c>
@@ -1039,8 +1102,11 @@
       <x:c r="X1" s="1">
         <x:v>46074</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:24">
+      <x:c r="Y1" s="1">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:25">
       <x:c r="F2" s="0">
         <x:v>42</x:v>
       </x:c>
@@ -1098,8 +1164,11 @@
       <x:c r="X2" s="0">
         <x:v>43</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:24">
+      <x:c r="Y2" s="0">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:25">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1160,13 +1229,16 @@
       <x:c r="X3" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:24">
+      <x:c r="Y3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:25">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -1175,15 +1247,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:25">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
@@ -1192,65 +1264,68 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:25">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:25">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -1259,36 +1334,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:25">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -1297,59 +1372,62 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:25">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="U9" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:24">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y9" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:25">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -1358,30 +1436,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:25">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -1390,18 +1468,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:24">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:25">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -1410,45 +1488,45 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:25">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
@@ -1457,98 +1535,101 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:25">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X14" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y14" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:25">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
@@ -1557,30 +1638,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:25">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -1589,15 +1670,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:25">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -1606,39 +1687,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:25">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>1</x:v>
@@ -1647,85 +1728,91 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:25">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y19" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:25">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W20" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:24">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="Y20" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:25">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>1</x:v>
@@ -1734,147 +1821,156 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:25">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X22" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y22" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:25">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="V23" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:24">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="Y23" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:25">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S24" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:24">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Y24" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:25">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>1</x:v>
@@ -1883,15 +1979,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:25">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>1</x:v>
@@ -1900,24 +1996,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M26" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:24">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:25">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>2</x:v>
@@ -1926,39 +2022,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L27" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T27" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:24">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:25">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>2</x:v>
@@ -1967,15 +2063,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:25">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>2</x:v>
@@ -1984,79 +2080,85 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:24">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:25">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U30" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="V30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X30" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:25">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:24">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Y31" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:25">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>2</x:v>
@@ -2065,73 +2167,79 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:25">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U33" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:24">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y33" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:25">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="W34" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="X34" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:25">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>2</x:v>
@@ -2140,15 +2248,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:25">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>2</x:v>
@@ -2157,15 +2265,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:25">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>3</x:v>
@@ -2174,18 +2282,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L37" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:24">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:25">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>3</x:v>
@@ -2194,18 +2302,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:25">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>3</x:v>
@@ -2214,21 +2322,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V39" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:24">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:25">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>3</x:v>
@@ -2237,15 +2345,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:25">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>3</x:v>
@@ -2254,15 +2362,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:25">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>4</x:v>
@@ -2271,15 +2379,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:25">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>4</x:v>
@@ -2288,39 +2396,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L43" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="M43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q43" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="S43" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U43" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="V43" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:25">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>4</x:v>
@@ -2329,27 +2437,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L44" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:24">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:25">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>4</x:v>
@@ -2358,21 +2466,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L45" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:25">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>4</x:v>
@@ -2381,15 +2489,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:25">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>4</x:v>
@@ -2398,68 +2506,71 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:25">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X48" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:25">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>4</x:v>
@@ -2468,15 +2579,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:25">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>5</x:v>
@@ -2485,21 +2596,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L50" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:25">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
@@ -2508,30 +2619,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O51" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="R51" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="S51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V51" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:24">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:25">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>5</x:v>
@@ -2540,27 +2651,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="P52" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:24">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:25">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>6</x:v>
@@ -2569,18 +2680,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O53" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:24">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:25">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>6</x:v>
@@ -2589,42 +2700,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R54" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="S54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U54" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="V54" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:25">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>7</x:v>
@@ -2633,50 +2744,53 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L55" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M55" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:25">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="U56" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:24">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y56" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:25">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>7</x:v>
@@ -2685,21 +2799,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L57" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S57" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="T57" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:25">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>7</x:v>
@@ -2708,18 +2822,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L58" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M58" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:25">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>8</x:v>
@@ -2728,15 +2842,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M59" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:25">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>8</x:v>
@@ -2745,21 +2859,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q60" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="V60" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:24">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:25">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>8</x:v>
@@ -2768,21 +2882,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O61" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:25">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>8</x:v>
@@ -2791,18 +2905,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O62" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:24">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:25">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>9</x:v>
@@ -2811,41 +2925,44 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q63" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:24">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:25">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O64" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y64" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:25">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>9</x:v>
@@ -2854,15 +2971,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:25">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>9</x:v>
@@ -2871,15 +2988,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:25">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>9</x:v>
@@ -2888,18 +3005,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O67" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:25">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>9</x:v>
@@ -2908,15 +3025,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:25">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>9</x:v>
@@ -2925,132 +3042,141 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O69" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:25">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="O70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X70" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y70" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:25">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="O71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="S71" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V71" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="W71" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y71" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:25">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S72" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V72" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W72" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y72" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:25">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>10</x:v>
@@ -3059,76 +3185,82 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O73" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T73" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="U73" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:25">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="O74" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V74" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:24">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="Y74" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:25">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="O75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W75" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="X75" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y75" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:25">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>10</x:v>
@@ -3137,175 +3269,190 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O76" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:25">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="O77" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P77" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q77" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R77" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S77" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T77" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y77" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:25">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="O78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S78" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y78" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:25">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V79" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="X79" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:24">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="Y79" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:25">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="O80" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S80" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T80" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V80" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="W80" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X80" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y80" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:25">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="O81" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P81" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q81" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V81" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="W81" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y81" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:25">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>10</x:v>
@@ -3314,56 +3461,59 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O82" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S82" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:24">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:25">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q83" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="R83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V83" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X83" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:24">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="Y83" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:25">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>10</x:v>
@@ -3372,59 +3522,62 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="O84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S84" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W84" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X84" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:25">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="O85" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W85" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:24">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="Y85" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:25">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>11</x:v>
@@ -3433,18 +3586,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P86" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q86" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:25">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>11</x:v>
@@ -3453,53 +3606,56 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P87" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q87" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R87" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S87" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:25">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="P88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W88" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:24">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="Y88" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:25">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>11</x:v>
@@ -3508,18 +3664,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P89" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q89" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:25">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>11</x:v>
@@ -3528,56 +3684,59 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P90" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q90" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S90" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T90" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V90" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:24">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:25">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="P91" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q91" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R91" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S91" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U91" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:24">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y91" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:25">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>11</x:v>
@@ -3586,24 +3745,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P92" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="Q92" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R92" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S92" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:25">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>12</x:v>
@@ -3612,15 +3771,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q93" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:25">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>12</x:v>
@@ -3629,15 +3788,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q94" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:25">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>12</x:v>
@@ -3646,93 +3805,102 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q95" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R95" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:25">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q96" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="R96" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y96" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:25">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="Q97" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S97" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T97" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U97" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V97" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y97" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:25">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q98" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T98" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="U98" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V98" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y98" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:25">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>13</x:v>
@@ -3741,58 +3909,64 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R99" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S99" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:25">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R100" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S100" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y100" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:25">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R101" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S101" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y101" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:25">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>13</x:v>
@@ -3801,33 +3975,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="R102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="T102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="U102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X102" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:25">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>13</x:v>
@@ -3836,15 +4010,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R103" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:25">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>13</x:v>
@@ -3853,35 +4027,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R104" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S104" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:25">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R105" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y105" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:25">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>13</x:v>
@@ -3890,38 +4067,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R106" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:25">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R107" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S107" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V107" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:24">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="Y107" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:25">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>13</x:v>
@@ -3930,18 +4110,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R108" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="S108" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:25">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>13</x:v>
@@ -3950,15 +4130,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R109" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:25">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>14</x:v>
@@ -3967,35 +4147,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S110" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:25">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S111" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X111" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:24">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="Y111" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:25">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>14</x:v>
@@ -4004,35 +4187,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S112" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:25">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="S113" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W113" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:24">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="Y113" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:25">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>14</x:v>
@@ -4041,55 +4227,61 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S114" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V114" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:24">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:25">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="T115" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y115" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:25">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="T116" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X116" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:24">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="Y116" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:25">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>15</x:v>
@@ -4098,41 +4290,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T117" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:25">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X118" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y118" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:25">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>16</x:v>
@@ -4141,24 +4336,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="U119" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V119" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W119" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X119" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:25">
       <x:c r="A120" s="0">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>16</x:v>
@@ -4167,35 +4362,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U120" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:25">
       <x:c r="A121" s="0">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U121" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V121" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y121" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:25">
       <x:c r="A122" s="0">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>16</x:v>
@@ -4204,18 +4402,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="U122" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V122" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:25">
       <x:c r="A123" s="0">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>16</x:v>
@@ -4224,61 +4422,67 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="U123" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V123" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:25">
       <x:c r="A124" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U124" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y124" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:25">
       <x:c r="A125" s="0">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="V125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X125" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y125" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:25">
       <x:c r="A126" s="0">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>16</x:v>
@@ -4287,58 +4491,64 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U126" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:25">
       <x:c r="A127" s="0">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V127" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W127" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X127" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y127" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:25">
       <x:c r="A128" s="0">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V128" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W128" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y128" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:25">
       <x:c r="A129" s="0">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>17</x:v>
@@ -4347,72 +4557,81 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V129" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:25">
       <x:c r="A130" s="0">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W130" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X130" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y130" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:25">
       <x:c r="A131" s="0">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W131" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y131" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:25">
       <x:c r="A132" s="0">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W132" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="X132" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y132" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:25">
       <x:c r="A133" s="0">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>18</x:v>
@@ -4421,24 +4640,231 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="W133" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:24">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:25">
       <x:c r="A134" s="0">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="X134" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Y134" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:25">
+      <x:c r="A135" s="0">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D135" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y135" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:25">
+      <x:c r="A136" s="0">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D136" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y136" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:25">
+      <x:c r="A137" s="0">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D137" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y137" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:25">
+      <x:c r="A138" s="0">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D138" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y138" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:25">
+      <x:c r="A139" s="0">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D139" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y139" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:25">
+      <x:c r="A140" s="0">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D140" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y140" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:25">
+      <x:c r="A141" s="0">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D141" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y141" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:25">
+      <x:c r="A142" s="0">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D142" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y142" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:25">
+      <x:c r="A143" s="0">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D143" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y143" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:25">
+      <x:c r="A144" s="0">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D144" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y144" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:25">
+      <x:c r="A145" s="0">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D145" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y145" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:25">
+      <x:c r="A146" s="0">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D146" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y146" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
